--- a/server/data/answers.xlsx
+++ b/server/data/answers.xlsx
@@ -1,40 +1,201 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>login error occurred</t>
+  </si>
+  <si>
+    <t>trouble logging in to application</t>
+  </si>
+  <si>
+    <t>account signing and credentials support</t>
+  </si>
+  <si>
+    <t>password reset procedure</t>
+  </si>
+  <si>
+    <t>retrieve lost password</t>
+  </si>
+  <si>
+    <t>credentials profile update</t>
+  </si>
+  <si>
+    <t>payment issue and failures</t>
+  </si>
+  <si>
+    <t>credit card declined</t>
+  </si>
+  <si>
+    <t>billing history and receipts</t>
+  </si>
+  <si>
+    <t>account registration options</t>
+  </si>
+  <si>
+    <t>social media login registration</t>
+  </si>
+  <si>
+    <t>new profile setup rules</t>
+  </si>
+  <si>
+    <t>refund policy and requests</t>
+  </si>
+  <si>
+    <t>returns and chargebacks support</t>
+  </si>
+  <si>
+    <t>order disputes and cancellations</t>
+  </si>
+  <si>
+    <t>canceling your subscription</t>
+  </si>
+  <si>
+    <t>stop recurring membership auto-renew</t>
+  </si>
+  <si>
+    <t>delete paid account details</t>
+  </si>
+  <si>
+    <t>app crash troubleshooting</t>
+  </si>
+  <si>
+    <t>mobile platform system crash help</t>
+  </si>
+  <si>
+    <t>device compatibility warnings</t>
+  </si>
+  <si>
+    <t>updating account profile email</t>
+  </si>
+  <si>
+    <t>modify email login contact</t>
+  </si>
+  <si>
+    <t>username change restrictions</t>
+  </si>
+  <si>
+    <t>Clear browser cookies and cache, then restart the browser.</t>
+  </si>
+  <si>
+    <t>Try logging in via Incognito mode or a different browser.</t>
+  </si>
+  <si>
+    <t>Contact support to reset your locked login session.</t>
+  </si>
+  <si>
+    <t>Click on Forgot Password on the login screen to receive a reset link.</t>
+  </si>
+  <si>
+    <t>Contact system administrator to manually trigger a password reset mail.</t>
+  </si>
+  <si>
+    <t>Go to settings to update your username or passphrase.</t>
+  </si>
+  <si>
+    <t>Use an alternative payment method like PayPal or bank transfer.</t>
+  </si>
+  <si>
+    <t>Contact your bank to verify if international/online payments are blocked.</t>
+  </si>
+  <si>
+    <t>Check your monthly invoice inside the subscription panel.</t>
+  </si>
+  <si>
+    <t>Yes, you can register using Google, Apple, or your email address.</t>
+  </si>
+  <si>
+    <t>You can sign up using Facebook or other social platforms if enabled.</t>
+  </si>
+  <si>
+    <t>Registration requires a valid email and password confirmation.</t>
+  </si>
+  <si>
+    <t>Refunds can be requested within 14 days of purchase via your billing portal.</t>
+  </si>
+  <si>
+    <t>To request a transaction rollback, contact billing support directly.</t>
+  </si>
+  <si>
+    <t>Orders can only be modified or canceled before shipping.</t>
+  </si>
+  <si>
+    <t>Go to Account Settings &gt; Subscriptions &gt; Cancel to turn off auto-renew.</t>
+  </si>
+  <si>
+    <t>Submit a ticket to cancel your subscription auto-billing.</t>
+  </si>
+  <si>
+    <t>Deleting your profile will immediately terminate all paid subscriptions.</t>
+  </si>
+  <si>
+    <t>Try clearing app storage, updating to the latest version, or reinstalling the app.</t>
+  </si>
+  <si>
+    <t>Report the bug logs to developer team using the in-app help button.</t>
+  </si>
+  <si>
+    <t>Make sure your operating system meets the minimum hardware specifications.</t>
+  </si>
+  <si>
+    <t>You can update your email under Profile Settings &gt; Security &gt; Update Email.</t>
+  </si>
+  <si>
+    <t>Submit a request to change the email where you receive billing updates.</t>
+  </si>
+  <si>
+    <t>Your username is fixed but your profile contact details can be modified.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +203,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,123 +520,211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>login error occurred</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Clear browser cookies and cache, then restart the application.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>login error occurred</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Try logging in via Incognito mode or a different browser.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>login error occurred</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ensure your credentials are correct or reset your password if locked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>password reset procedure</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Click on Forgot Password on the login screen to receive a reset link.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>password reset procedure</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Contact system administrator to manually trigger a password reset mail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>payment issue</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Check if your credit card has sufficient funds and is active.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>payment issue</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Contact your bank to verify if international/online payments are blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>payment issue</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Use an alternative payment method like PayPal or bank transfer.</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>